--- a/cartographie/cartographie_filiere.xlsx
+++ b/cartographie/cartographie_filiere.xlsx
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Industriels'!$A$1:$G$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Marques'!$A$1:$E$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Alias'!$A$1:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Agences'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Agences'!$A$1:$F$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Influenceurs'!$A$1:$F$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sources_de_donnees'!$A$1:$F$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'HATVP_organisations'!$A$1:$O$36</definedName>
@@ -13085,7 +13085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13252,8 +13252,68 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Webedia</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>INAPORC</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Lives Twitch sur le metier d'eleveur de porcs</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Gastronogeek (live cuisine, best-of sur sa chaine YouTube) et LeBouseuh (defi Minecraft sur l'elevage porcin, best-of egalement). Cible declaree : 18-30 ans. Deux createurs generalistes.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>leporc.com/le-porc-en-france/le-metier-d-eleveur-de-porcs-mis-en-lumiere-sur-twitch</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>INAPORC</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Les recettes des influenceurs (programme suivi)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Au moins 92 recettes creditees a des createurs nommes, avec notice biographique publiee par INAPORC : Mercotte, pepites2noisette (32 recettes), olivier.moulin (19), juliamaufay (13), mummyfast (12), menthe_banane, sophiecuisine, julienduboue, woodmoodfood, florianonair, chateau.leg0, agatheduchesne_, Dorian, Audrey.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>leporc.com/recettes/la-cuisine-des-influenceurs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/cartographie/cartographie_filiere.xlsx
+++ b/cartographie/cartographie_filiere.xlsx
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Industriels'!$A$1:$G$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Marques'!$A$1:$E$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Alias'!$A$1:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Agences'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Agences'!$A$1:$F$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Influenceurs'!$A$1:$F$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sources_de_donnees'!$A$1:$F$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'HATVP_organisations'!$A$1:$O$36</definedName>
@@ -13085,7 +13085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13285,35 +13285,255 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>iProspect Conseil France</t>
+        </is>
+      </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Publicite TikTok (26 annonces)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Agence declaree par TikTok comme payeur des annonces INTERBEV. Aucun createur associe : l'API ne relie pas annonceur et createur.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>API TikTok ad/query, champ advertiser.paid_for_by, 25/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Publicis Media - Starcom</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Groupe Bel</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Publicite TikTok (56 annonces)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Babybel, Kiri, La Vache qui rit. Agence declaree payeur.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>API TikTok ad/query, 25/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>WPP MEDIA FRANCE</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Danone / Yoplait / Nestle</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Publicite TikTok</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Meme agence declaree pour Danone Produits Frais (17), Yoplait (60) et Nestle France. Actimel, Activia.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>API TikTok ad/query, 25/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>VMLY&amp;R France</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Nestle France</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Publicite TikTok (38 annonces)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Sort sur les termes « lait », « viande » et « Charal ».</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>API TikTok ad/query, 25/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Havas Media France</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Lactalis</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Publicite TikTok</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Marque Lactel.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>API TikTok ad/query, 25/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Publicis Media - Blue449</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Savencia</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Publicite TikTok</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Caprice des Dieux.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>API TikTok ad/query, 25/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Vanksen</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Candia (Sodiaal)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Publicite TikTok (8 annonces)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>API TikTok ad/query, 25/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>INAPORC</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Les recettes des influenceurs (programme suivi)</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Au moins 92 recettes creditees a des createurs nommes, avec notice biographique publiee par INAPORC : Mercotte, pepites2noisette (32 recettes), olivier.moulin (19), juliamaufay (13), mummyfast (12), menthe_banane, sophiecuisine, julienduboue, woodmoodfood, florianonair, chateau.leg0, agatheduchesne_, Dorian, Audrey.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>CONFIRME</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>leporc.com/recettes/la-cuisine-des-influenceurs</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
+  <autoFilter ref="A1:F14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/cartographie/cartographie_filiere.xlsx
+++ b/cartographie/cartographie_filiere.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Interprofessions'!$A$1:$H$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Industriels'!$A$1:$G$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Marques'!$A$1:$E$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Alias'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Alias'!$A$1:$E$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Agences'!$A$1:$F$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Influenceurs'!$A$1:$F$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sources_de_donnees'!$A$1:$F$15</definedName>
@@ -12736,7 +12736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -12951,32 +12951,36 @@
       <c r="E8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Le Porc Francais</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>marque filiere</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>INAPORC</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>A VERIFIER</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>En Mode Actif</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>nom de campagne</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Campagne COFINANCEE PAR L'UNION EUROPEENNE, contre la sedentarite. Nommee par Studio Danielle (1,74 M d'abonnes) dans deux descriptions : « en partenariat avec Les Produits Laitiers et leur campagne En Mode Actif cofinancee par l'UE ». Decouverte le 26/08/2026, absente de la table jusque-la. Le cofinancement europeen relie au dossier AGRIP.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Volaille Francaise</t>
+          <t>Le Porc Francais</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -12986,7 +12990,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>INAPORC</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -12999,82 +13003,105 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>Volaille Francaise</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>marque filiere</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>ANVOL</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>Oeufs de France</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>marque filiere</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>CNPO</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>A VERIFIER</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>@lescereales</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>compte vitrine</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Intercereales</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>CONFIRME</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>HORS PERIMETRE. Groupe temoin pour tester la detection.</t>
-        </is>
-      </c>
+      <c r="E12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>@lescereales</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>compte vitrine</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Intercereales</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>HORS PERIMETRE. Groupe temoin pour tester la detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>@cetepimepate</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>compte vitrine</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>FNPSMS</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>CONFIRME</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>HORS PERIMETRE. Groupe temoin.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/cartographie/cartographie_filiere.xlsx
+++ b/cartographie/cartographie_filiere.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Interprofessions'!$A$1:$H$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Industriels'!$A$1:$G$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Marques'!$A$1:$E$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Alias'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Alias'!$A$1:$E$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Agences'!$A$1:$F$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Influenceurs'!$A$1:$F$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sources_de_donnees'!$A$1:$F$15</definedName>
@@ -12736,7 +12736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -12953,57 +12953,61 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Made in Viande</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>nom d'operation</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Portes ouvertes annuelles de la filiere elevage et viande. Nommee dans les descriptions de FlorianOnAir (734 k abonnes), jugees collaborations remunerees par Vincent. Absente de la table jusqu'au 26/08/2026 : la detection attrapait ces videos par appariement approximatif, sans savoir ce qu'etait l'operation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>En Mode Actif</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>nom de campagne</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>CNIEL</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>CONFIRME</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Campagne COFINANCEE PAR L'UNION EUROPEENNE, contre la sedentarite. Nommee par Studio Danielle (1,74 M d'abonnes) dans deux descriptions : « en partenariat avec Les Produits Laitiers et leur campagne En Mode Actif cofinancee par l'UE ». Decouverte le 26/08/2026, absente de la table jusque-la. Le cofinancement europeen relie au dossier AGRIP.</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Le Porc Francais</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>marque filiere</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>INAPORC</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>A VERIFIER</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Volaille Francaise</t>
+          <t>Le Porc Francais</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -13013,7 +13017,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ANVOL</t>
+          <t>INAPORC</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -13026,82 +13030,105 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>Volaille Francaise</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>marque filiere</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>ANVOL</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>Oeufs de France</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>marque filiere</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>CNPO</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>A VERIFIER</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>@lescereales</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>compte vitrine</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Intercereales</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>CONFIRME</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>HORS PERIMETRE. Groupe temoin pour tester la detection.</t>
-        </is>
-      </c>
+      <c r="E13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>@lescereales</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>compte vitrine</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Intercereales</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>HORS PERIMETRE. Groupe temoin pour tester la detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>@cetepimepate</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>compte vitrine</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>FNPSMS</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>CONFIRME</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>HORS PERIMETRE. Groupe temoin.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E14"/>
+  <autoFilter ref="A1:E15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/cartographie/cartographie_filiere.xlsx
+++ b/cartographie/cartographie_filiere.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Interprofessions'!$A$1:$H$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Industriels'!$A$1:$G$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Marques'!$A$1:$E$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Alias'!$A$1:$E$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Alias'!$A$1:$E$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Agences'!$A$1:$F$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Influenceurs'!$A$1:$F$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sources_de_donnees'!$A$1:$F$15</definedName>
@@ -12736,7 +12736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -12953,17 +12953,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Made in Viande</t>
+          <t>LAITFLIX</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>nom d'operation</t>
+          <t>nom de serie</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
+          <t>CNIEL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -12973,19 +12973,19 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Portes ouvertes annuelles de la filiere elevage et viande. Nommee dans les descriptions de FlorianOnAir (734 k abonnes), jugees collaborations remunerees par Vincent. Absente de la table jusqu'au 26/08/2026 : la detection attrapait ces videos par appariement approximatif, sans savoir ce qu'etait l'operation.</t>
+          <t>Serie de videos de divertissement du CNIEL, hebergee sur produits-laitiers.com. Playlists nommant des createurs : « ON DEVIENT FERMIER 48H DANS LES MONTAGNES Feat Inoxtag », « Mister V : les copains au lait », « Billy et Amine decouvrent les specialites de nos regions », « La ferme des celebrites ». Trouvee par Vincent le 27/08/2026.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>En Mode Actif</t>
+          <t>Les copains au lait</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>nom de campagne</t>
+          <t>nom de serie</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -13000,93 +13000,105 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Campagne COFINANCEE PAR L'UNION EUROPEENNE, contre la sedentarite. Nommee par Studio Danielle (1,74 M d'abonnes) dans deux descriptions : « en partenariat avec Les Produits Laitiers et leur campagne En Mode Actif cofinancee par l'UE ». Decouverte le 26/08/2026, absente de la table jusque-la. Le cofinancement europeen relie au dossier AGRIP.</t>
+          <t>Serie LAIT'FLIX avec Mister V (6,53 M d'abonnes). Huit videos reperees sur la chaine YouTube du CNIEL.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Le Porc Francais</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>marque filiere</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>INAPORC</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>A VERIFIER</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>L'Amour Boeuf</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>nom de serie</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Serie de videos sur la filiere, hebergee sur la-viande.fr. Compte @lamourboeuf deja repere dans les abonnements d'INTERBEV.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Volaille Francaise</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>marque filiere</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>ANVOL</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>A VERIFIER</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>@foiegrasfrancais</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>compte vitrine</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>CIFOG</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Instagram, 20 900 abonnes. Trouve par Vincent le 27/08. **Doit remplacer l'alias « Le Foie Gras »**, qui designe l'aliment et a produit 91 candidats pour zero vrai (JOURNAL 38.2).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Oeufs de France</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>marque filiere</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>CNPO</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>A VERIFIER</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Produits Laitiers</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>chaine YouTube</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Chaine officielle du CNIEL, 101 000 abonnes, 132 videos. UCOkKpH6tIRaNKPsNB7a3r3w</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>@lescereales</t>
+          <t>Aimez la viande</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>compte vitrine</t>
+          <t>chaine YouTube</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Intercereales</t>
+          <t>INTERBEV</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -13096,39 +13108,270 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>HORS PERIMETRE. Groupe temoin pour tester la detection.</t>
+          <t>Chaine officielle d'INTERBEV, 79 500 abonnes, 292 videos. UCGVLdT9d5MIDrqiiMDht-jg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>@volaillefrancaise8086</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>chaine YouTube</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>ANVOL</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Chaine officielle d'ANVOL, 236 abonnes, 40 videos. Lien avec FlorianOnAir signale par Vincent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>@LeFoieGrasFrance</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>chaine YouTube</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>CIFOG</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Chaine officielle du CIFOG, 788 abonnes, 197 videos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>INTERBEV Nouvelle-Aquitaine</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>chaine YouTube regionale</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Une des structures regionales. D'autres existent : Occitanie, Grand Est, Pays de la Loire — leurs comptes restent a relever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Made in Viande</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>nom d'operation</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Portes ouvertes annuelles de la filiere elevage et viande. Nommee dans les descriptions de FlorianOnAir (734 k abonnes), jugees collaborations remunerees par Vincent. Absente de la table jusqu'au 26/08/2026 : la detection attrapait ces videos par appariement approximatif, sans savoir ce qu'etait l'operation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>En Mode Actif</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>nom de campagne</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Campagne COFINANCEE PAR L'UNION EUROPEENNE, contre la sedentarite. Nommee par Studio Danielle (1,74 M d'abonnes) dans deux descriptions : « en partenariat avec Les Produits Laitiers et leur campagne En Mode Actif cofinancee par l'UE ». Decouverte le 26/08/2026, absente de la table jusque-la. Le cofinancement europeen relie au dossier AGRIP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Le Porc Francais</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>marque filiere</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>INAPORC</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Volaille Francaise</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>marque filiere</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>ANVOL</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Oeufs de France</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>marque filiere</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>CNPO</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>@lescereales</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>compte vitrine</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Intercereales</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>HORS PERIMETRE. Groupe temoin pour tester la detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>@cetepimepate</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>compte vitrine</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>FNPSMS</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>CONFIRME</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>HORS PERIMETRE. Groupe temoin.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E15"/>
+  <autoFilter ref="A1:E24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/cartographie/cartographie_filiere.xlsx
+++ b/cartographie/cartographie_filiere.xlsx
@@ -20,6 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HATVP_mandats" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HATVP_affiliations" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta_annonceurs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medias" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LISEZ-MOI'!$A$1:$B$14</definedName>
@@ -42,7 +43,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +59,19 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +86,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FBEFD6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00434343"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -105,6 +122,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -10100,6 +10120,681 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>A QUOI SERT CETTE FEUILLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Les comptes listes ici sont ECARTES automatiquement des candidats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Ce sont des medias, des emissions ou des plateformes : ils parlent de viande et de lait pour des raisons journalistiques, pas commerciales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Avant le 27/08/2026 cette liste etait ecrite DANS LE CODE, en deux copies differentes. Vincent ne pouvait pas l'amender. Elle vit ici desormais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>POUR AJOUTER UN MEDIA : ecris son nom dans la colonne A, une ligne par media. La casse et les accents n'ont pas d'importance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>RESERVE IMPORTANTE : un media PEUT etre remunere par un lobby, et ce serait un fait interessant. Mais c'est une autre enquete, et melanger les deux noierait les deux. Si on veut la mener, on le fera separement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>nom_du_media</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>pourquoi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20 minutes</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>amazon prime video france</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>plateforme</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>arte</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>bfmtv</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>brut</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>c a vous</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>emission de television</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>c_a_vous</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>emission de television</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>canal+</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cnews</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cuisine actuelle</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>site de recettes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>deezer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>plateforme</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>disney+</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>plateforme</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>europe 1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>france 2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>france 24</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>france 3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>france 5</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>franceinfo</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>huffpost</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>konbini</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>l'equipe</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>la depeche</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>lci</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>le figaro</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>le monde</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>le parisien</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>lemondefr</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>lequipe</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>liberation</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>m6</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>marmiton</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>site de recettes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>minecraft</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>jeu video</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>national geographic</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>netflix france</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>plateforme</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>olympic games</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>evenement sportif</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>olympics</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>evenement sportif</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ouest-france</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>prime video france</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>plateforme</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>rmc</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>rtl</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>slate</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>spotify</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>plateforme</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>sud ouest</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>tf1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>top chef</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>emission de television</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>topchefm6</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>emission de television</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>vice</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>media d'information</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>wimbledon</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>evenement sportif</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>plateforme</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/cartographie/cartographie_filiere.xlsx
+++ b/cartographie/cartographie_filiere.xlsx
@@ -13431,7 +13431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -14062,6 +14062,546 @@
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>HORS PERIMETRE. Groupe temoin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CHAUD !</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>nom de serie</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Serie LAIT'FLIX. L'episode « ON DEVIENT FERMIER 48H DANS LES MONTAGNES Feat Inoxtag » porte « En partenariat avec Les Produits Laitiers » en description — Vincent, 26/08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Billy et Amine decouvrent les specialites de nos regions</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>nom de serie</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Serie LAIT'FLIX. Amine = @Aminematue, 1,98 M d'abonnes YouTube.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>La ferme des celebrites</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>nom de serie</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Serie LAIT'FLIX. Plusieurs createurs connus selon Vincent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>La Carotte d'Avner</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>nom de serie</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Serie LAIT'FLIX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Morgane decouvre les AOP</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>nom de serie</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Serie LAIT'FLIX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Le Tour du Monde de Loris</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>nom de serie</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Serie LAIT'FLIX. Loris = LORIS GIULIANO, 35 preuves fortes deja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Le Tour de France de Loris</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>nom de serie</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Serie LAIT'FLIX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Myriam met du beurre dans tes epinards</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>nom de serie</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Serie LAIT'FLIX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>We.Love Agri</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>nom de serie</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Serie video sur la-viande.fr, relevee par Vincent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>@lifeatdanone</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>compte de marque</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Danone</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Seul compte Danone trouve. Vincent : « pas sur que ce soit francais ». Il n'existe PAS de @danone.france.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>@nestleenfrance</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>compte de marque</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Nestle France</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Verifie par Vincent le 26/08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>@savencia_groupe</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>compte de marque</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Savencia</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Verifie par Vincent le 26/08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>@herta_france</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>compte de marque</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Herta (Nestle)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Deja present dans les abonnements d'INAPORC, 13 contenus commerciaux TikTok.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>@legaulois_officiel</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compte de marque</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Le Gaulois (LDC)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Verifie par Vincent le 26/08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>@charal_officiel</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>compte de marque</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Charal (Bigard)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Verifie par Vincent le 26/08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>@charal_france</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>compte de marque</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Charal (Bigard)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Second compte Charal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>@interbev_paysdelaloire</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>compte regional</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Releve par Vincent le 26/08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>@interbevidf</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>compte regional</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Releve par Vincent le 26/08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>@interbevgrandest</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>compte regional</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Releve par Vincent le 26/08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>@interbevcentre</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>compte regional</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Releve par Vincent le 26/08.</t>
         </is>
       </c>
     </row>

--- a/cartographie/cartographie_filiere.xlsx
+++ b/cartographie/cartographie_filiere.xlsx
@@ -13431,7 +13431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -14602,6 +14602,411 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>Releve par Vincent le 26/08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Blind Dates avec Cyril Lignac</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>nom de serie</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Serie sur la-viande.fr. Cyril Lignac y recoit des professionnels de la filiere. Releve le 28/08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Le Boeuf Cooking Show</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>nom de serie</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Serie sur la-viande.fr — « l'emission qui taille bavette ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bienvenue chez les Jolipre</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>nom de serie</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Serie sur la-viande.fr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Le Mois de la Volaille Francaise</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>nom de campagne</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ANVOL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Campagne sur volaille-francaise.fr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Les Volaillissimes</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>nom de campagne</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ANVOL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Campagne ANVOL. Deja vue dans la moisson de la chaine YouTube (17 videos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Volailles Festives</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>nom de campagne</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ANVOL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Campagne sur volaille-francaise.fr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>La Volaille Francaise a la Baguette</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>nom de campagne</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ANVOL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Campagne sur volaille-francaise.fr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>@leblogdufoiegras</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>compte vitrine</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CIFOG</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Chaine YouTube du CIFOG, indiquee sur lefoiegras.fr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>@FandeFoieGras</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>compte vitrine</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CIFOG</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Facebook et Twitter du CIFOG. La page Facebook a paye 81 annonces moissonnees le 27/08, dont quatre nommant @megalowfood.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>@lavolaillefrancaise</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>compte vitrine</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ANVOL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Facebook d'ANVOL, indique sur volaille-francaise.fr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>jaimelavolaille.fr</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>site vitrine</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ANVOL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Site de recettes d'ANVOL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>jaimeladinde.fr</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>site vitrine</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ANVOL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Site d'ANVOL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>volaille-info.fr</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>site vitrine</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ANVOL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Site d'ANVOL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>interpro-anvol.fr</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>site institutionnel</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ANVOL</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Site institutionnel d'ANVOL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Association de Promotion de la Volaille Francaise</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ANVOL</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>APVF — structure de promotion citee sur volaille-francaise.fr.</t>
         </is>
       </c>
     </row>

--- a/cartographie/cartographie_filiere.xlsx
+++ b/cartographie/cartographie_filiere.xlsx
@@ -10801,7 +10801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11315,6 +11315,36 @@
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Paye Ton Influence, LinkedIn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FICT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Federation Francaise des Industriels Charcutiers Traiteurs</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Charcuterie</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Quatrieme lobby etudie par Greenpeace France aux cotes d'INTERBEV, INAPORC et ANVOL. Absent de la table jusqu'au 28/08. RAPPORTE : rapport Greenpeace « Lobbies de la viande ».</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>greenpeace.fr</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -15007,6 +15037,114 @@
       <c r="E59" t="inlineStr">
         <is>
           <t>APVF — structure de promotion citee sur volaille-francaise.fr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>A table avec les Jolipre</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>nom de campagne</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAPPORTE — Greenpeace : serie TV, bandes dessinees et livrets, touchant 508 985 enfants de 6 a 11 ans dans 999 communes entre 2016 et 2019. Le site la-viande.fr porte une variante « Bienvenue chez les Jolipre ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Let's talk about pork</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>nom de campagne</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>INAPORC</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAPPORTE — Greenpeace : campagne europeenne ayant touche 74 millions de millennials en 2020.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Sante : n'oubliez pas la viande</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>nom de campagne</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAPPORTE — Greenpeace : 7 900 salles d'attente, 22 millions de patients, 2016.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Radio Sexe</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>nom d'emission</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAPPORTE — StreetPress : episode sponsorise du podcast de Kameto et Zack Nani, tourne en Coree, voyage finance par le CNIEL. Alias fragile : le titre n'a aucun rapport lexical avec la filiere.</t>
         </is>
       </c>
     </row>

--- a/cartographie/cartographie_filiere.xlsx
+++ b/cartographie/cartographie_filiere.xlsx
@@ -11334,14 +11334,11 @@
           <t>Charcuterie</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>Quatrieme lobby etudie par Greenpeace France aux cotes d'INTERBEV, INAPORC et ANVOL. Absent de la table jusqu'au 28/08. RAPPORTE : rapport Greenpeace « Lobbies de la viande ».</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>greenpeace.fr</t>
@@ -13461,7 +13458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -15145,6 +15142,33 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>RAPPORTE — StreetPress : episode sponsorise du podcast de Kameto et Zack Nani, tourne en Coree, voyage finance par le CNIEL. Alias fragile : le titre n'a aucun rapport lexical avec la filiere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Nature de Breton</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>marque</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Nature de Breton (beurre, Bretagne)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>MESURE du 29/08 : quatre videos de Lebouseuh portent la marque en description, dont « 24H A LA FERME ! » (visite de ferme et de beurrerie, 03/06/2023) et « ROADTRIP DANS LA MEILLEURE REGION DE FRANCE ». Trouvee en cherchant tout autre chose : le best-of INAPORC. Voir JOURNAL 70.</t>
         </is>
       </c>
     </row>

--- a/cartographie/cartographie_filiere.xlsx
+++ b/cartographie/cartographie_filiere.xlsx
@@ -11160,7 +11160,7 @@
       <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Hors perimetre strict viande/lait : inclusion a trancher.</t>
+          <t>DANS LE PERIMETRE depuis le 29/08/2026. Decision de Vincent : « elargissons notre scope aux oeufs », apres avoir trouve @fans_doeufs, compte Instagram de la vitrine Oeufs de France, 16 700 abonnes. L'oeuf etait exclu depuis le 22/08 par METHODOLOGIE section 1.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -13458,7 +13458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -15169,6 +15169,33 @@
       <c r="E64" t="inlineStr">
         <is>
           <t>MESURE du 29/08 : quatre videos de Lebouseuh portent la marque en description, dont « 24H A LA FERME ! » (visite de ferme et de beurrerie, 03/06/2023) et « ROADTRIP DANS LA MEILLEURE REGION DE FRANCE ». Trouvee en cherchant tout autre chose : le best-of INAPORC. Voir JOURNAL 70.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>@fans_doeufs</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>compte vitrine</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>CNPO</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CONFIRME</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Compte Instagram de la vitrine Oeufs de France, 16 700 abonnes. Trouve par Vincent le 29/08.</t>
         </is>
       </c>
     </row>
